--- a/data/teste_agendameto.xlsx
+++ b/data/teste_agendameto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arthur.machado\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olam-my.sharepoint.com/personal/arthur_machado_ofi_com/Documents/Documentos/GitHub/teste_copilot_app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D83CFA-E7E2-48BF-948C-01EE8038C180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{45D83CFA-E7E2-48BF-948C-01EE8038C180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92D36402-359B-4F08-AAA4-8B80711E96DD}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{DC880A8C-13E8-4B8D-B84E-6B4978047A04}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DC880A8C-13E8-4B8D-B84E-6B4978047A04}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="162">
   <si>
     <t>CHEGADA</t>
   </si>
@@ -1010,7 +1010,7 @@
         <v>220</v>
       </c>
       <c r="F4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G4" t="s">
         <v>156</v>
@@ -1033,7 +1033,7 @@
         <v>220</v>
       </c>
       <c r="F5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G5" t="s">
         <v>156</v>
@@ -1056,7 +1056,7 @@
         <v>440</v>
       </c>
       <c r="F6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G6" t="s">
         <v>157</v>
@@ -1079,7 +1079,7 @@
         <v>220</v>
       </c>
       <c r="F7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G7" t="s">
         <v>157</v>
@@ -1102,7 +1102,7 @@
         <v>220</v>
       </c>
       <c r="F8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G8" t="s">
         <v>157</v>
@@ -1125,7 +1125,7 @@
         <v>350</v>
       </c>
       <c r="F9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G9" t="s">
         <v>156</v>
@@ -1148,7 +1148,7 @@
         <v>230</v>
       </c>
       <c r="F10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G10" t="s">
         <v>156</v>
@@ -1196,6 +1196,9 @@
       <c r="F12" t="s">
         <v>160</v>
       </c>
+      <c r="G12" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1216,6 +1219,9 @@
       <c r="F13" t="s">
         <v>160</v>
       </c>
+      <c r="G13" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1235,6 +1241,9 @@
       </c>
       <c r="F14" t="s">
         <v>160</v>
+      </c>
+      <c r="G14" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
